--- a/artfynd/S 2314-2025 artfynd.xlsx
+++ b/artfynd/S 2314-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597024</v>
       </c>
       <c r="B2" t="n">
-        <v>100815</v>
+        <v>100863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135597036</v>
       </c>
       <c r="B3" t="n">
-        <v>99233</v>
+        <v>99280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135597017</v>
       </c>
       <c r="B4" t="n">
-        <v>106141</v>
+        <v>106196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2314-2025 artfynd.xlsx
+++ b/artfynd/S 2314-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597024</v>
       </c>
       <c r="B2" t="n">
-        <v>100863</v>
+        <v>100890</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135597036</v>
       </c>
       <c r="B3" t="n">
-        <v>99280</v>
+        <v>99307</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135597017</v>
       </c>
       <c r="B4" t="n">
-        <v>106196</v>
+        <v>106223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2314-2025 artfynd.xlsx
+++ b/artfynd/S 2314-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597024</v>
       </c>
       <c r="B2" t="n">
-        <v>100895</v>
+        <v>100897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135597036</v>
       </c>
       <c r="B3" t="n">
-        <v>99312</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135597017</v>
       </c>
       <c r="B4" t="n">
-        <v>106228</v>
+        <v>106230</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2314-2025 artfynd.xlsx
+++ b/artfynd/S 2314-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597024</v>
       </c>
       <c r="B2" t="n">
-        <v>100897</v>
+        <v>100914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135597036</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135597017</v>
       </c>
       <c r="B4" t="n">
-        <v>106230</v>
+        <v>106250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2314-2025 artfynd.xlsx
+++ b/artfynd/S 2314-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597024</v>
       </c>
       <c r="B2" t="n">
-        <v>100914</v>
+        <v>100916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135597036</v>
       </c>
       <c r="B3" t="n">
-        <v>99331</v>
+        <v>99332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135597017</v>
       </c>
       <c r="B4" t="n">
-        <v>106250</v>
+        <v>106252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 2314-2025 artfynd.xlsx
+++ b/artfynd/S 2314-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135597024</v>
       </c>
       <c r="B2" t="n">
-        <v>100916</v>
+        <v>100917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135597036</v>
       </c>
       <c r="B3" t="n">
-        <v>99332</v>
+        <v>99333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135597017</v>
       </c>
       <c r="B4" t="n">
-        <v>106252</v>
+        <v>106253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
